--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Drar 1 extra personkort varje kvartal</t>
+          <t>Drar 1 extra nätverkskort varje kvartal</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Lägg en dold plusbricka på en egen hyresrätt varje kvartal.</t>
+          <t>Underhållsvarningar på hyresrätter kostar inget att röja.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Briljant vid förhandlingsbordet, men otålig med tekniken.</t>
+          <t>Får hyresgäster att skriva på innan kaffet hunnit kallna och vet exakt när motparten är redo att ge sig. På kontorsmarknaden är ingen bättre. En värmepump är däremot en svart låda, och energikalkylen lämnas gärna till någon annan.</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Kan energisystemen utan och innan, mindre vass i affären.</t>
+          <t>Kan varje fastighets ventilationsaggregat vid namn och ser energiklassen på långt håll. Förskolor är favoriterna, där finns alltid något att förbättra. I förhandlingsrummet blir det däremot lätt för mycket detaljer och för lite affär.</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tar smällarna utan att blinka.</t>
+          <t>Tar smällarna utan att blinka och har alltid en plan B, helst en plan C också. Lokaler med krångliga hyresgäster är specialiteten. Aldrig spektakulär, aldrig panik, men aldrig heller den som vinner budgivningen.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Har sett fler stambyten än någon annan och vet vad som kan vänta.</t>
+          <t>Har varit med om fler stambyten än någon annan och vet vad som väntar bakom kaklet. Hyresrätterna sköts tryggt och utan dramatik. Förutsägbart, stabilt och ärligt talat lite trist, precis som det ska vara.</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Har fler kontakter än de andra, i rätt korridorer.</t>
+          <t>Har fler kontakter än de andra, och de sitter i rätt korridorer på kommersiella fastighetsmarknaden. Alltid på väg till nästa lunch. Bostadsaffärer tycker hen är lite för små för att riktigt engagera sig i.</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -744,7 +744,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Metodisk och förutseende, bygger alltid in en marginal.</t>
+          <t>Metodisk och förutseende, bygger alltid in en marginal och har aldrig bråttom. Budgeten har en rad för det oväntade, och den är aldrig tom. Tar sällan de stora chanserna, men förlorar heller aldrig huset.</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Drar 1 extra nätverkskort varje kvartal</t>
+          <t>Drar 1 extra nätverkskort varje kvartal och får ha 8 kort på hand</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LOKAL</t>
+          <t>LOKAL, KONTOR, FÖRSKOLA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>En gång per kvartal: ignorera ett händelsekort med minus, varning eller direkt minus på en lokal</t>
+          <t>En gång per kvartal: ignorera ett händelsekort med minus, varning eller direkt minus på en lokal, ett kontor eller en förskola</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tar smällarna utan att blinka och har alltid en plan B, helst en plan C också. Lokaler med krångliga hyresgäster är specialiteten. Aldrig spektakulär, aldrig panik, men aldrig heller den som vinner budgivningen.</t>
+          <t>Tar smällarna utan att blinka och har alltid en plan B, helst en plan C också. Kommersiella fastigheter med krångliga hyresgäster är specialiteten. Aldrig spektakulär, aldrig panik, men aldrig heller den som vinner budgivningen.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Underhållsvarningar på hyresrätter ger straff först vid 4, och kostar 1 Mkr mindre att röja</t>
+          <t>En gång per kvartal: gör ett negativt händelsekort på en hyresrätt till en underhållsvarning i stället. Varningar på hyresrätter ger straff först vid 4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Underhållsvarningar på hyresrätter kostar inget att röja.</t>
+          <t>Två gånger per kvartal.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>En gång per kvartal: ignorera ett händelsekort med minus, varning eller direkt minus på en lokal, ett kontor eller en förskola</t>
+          <t>En gång per kvartal: ignorera ett negativt händelsekort på en lokal, ett kontor eller en förskola</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Två gånger per kvartal.</t>
+          <t>Två gånger per kvartal blir ett negativt händelsekort på en hyresrätt en underhållsvarning i stället.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">

--- a/kortdata/F_FC.xlsx
+++ b/kortdata/F_FC.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Svagheten försvinner. En gång per kvartal: förstaval på ett kontor utan att slå.</t>
+          <t>Svagheten försvinner. +5 på förhandlingsslag om kontor.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Svagheten försvinner. Första uppgraderingsförsöket varje kvartal är gratis.</t>
+          <t>Svagheten försvinner. Uppgraderingsförsök kostar 2 Mkr i stället för 3.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>En gång per kvartal: ignorera ett negativt händelsekort på en lokal, ett kontor eller en förskola</t>
+          <t>En gång per kvartal (vrid kortet): ignorera ett negativt händelsekort på en lokal, ett kontor eller en förskola</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>En gång per kvartal: gör ett negativt händelsekort på en hyresrätt till en underhållsvarning i stället. Varningar på hyresrätter ger straff först vid 4</t>
+          <t>En gång per kvartal (vrid kortet): negativt händelsekort på hyresrätt blir underhållsvarning. Straff först vid 4 varningar</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Två gånger per kvartal blir ett negativt händelsekort på en hyresrätt en underhållsvarning i stället.</t>
+          <t>Som junior, och ni tar en riskbuffert varje gång förmågan används.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
